--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2889-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2889-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9A23D26-0FEC-4F6D-889A-816589EE0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4A0C287-20D6-4DBC-A98C-BE9D3B71593D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{8C2CE68D-ACE3-4CAA-B43C-982EBE3A11A9}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{0ADD8579-C959-43AE-9093-48AA54FE30BB}"/>
   </bookViews>
   <sheets>
     <sheet name="2889-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1559,29 +1559,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFD35BF1-41FA-468A-B30E-A13136759C02}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10C3E258-66FA-4E00-AB73-F9519E3EA3DD}">
   <dimension ref="A1:X33"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1615,7 +1614,7 @@
       <c r="W1" s="31"/>
       <c r="X1" s="23"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1651,7 +1650,7 @@
       <c r="W2" s="33"/>
       <c r="X2" s="34"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1703,7 +1702,7 @@
       </c>
       <c r="X3" s="37"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1771,7 +1770,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>2024</v>
       </c>
@@ -1843,7 +1842,7 @@
         <v>5.04</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="40">
         <v>2023</v>
       </c>
@@ -1915,7 +1914,7 @@
         <v>8.34</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>2022</v>
       </c>
@@ -1987,7 +1986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="42">
         <v>2021</v>
       </c>
@@ -2059,7 +2058,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="44"/>
       <c r="B9" s="45"/>
       <c r="C9" s="18" t="s">
@@ -2087,7 +2086,7 @@
       <c r="W9" s="51"/>
       <c r="X9" s="47"/>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="52">
         <v>2020</v>
       </c>
@@ -2159,7 +2158,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="54"/>
       <c r="B11" s="55"/>
       <c r="C11" s="20" t="s">
@@ -2187,7 +2186,7 @@
       <c r="W11" s="61"/>
       <c r="X11" s="57"/>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="42">
         <v>2019</v>
       </c>
@@ -2259,7 +2258,7 @@
         <v>9.49</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="44"/>
       <c r="B13" s="45"/>
       <c r="C13" s="18" t="s">
@@ -2287,7 +2286,7 @@
       <c r="W13" s="51"/>
       <c r="X13" s="47"/>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="52">
         <v>2018</v>
       </c>
@@ -2359,7 +2358,7 @@
         <v>5.81</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="54"/>
       <c r="B15" s="55"/>
       <c r="C15" s="20" t="s">
@@ -2387,7 +2386,7 @@
       <c r="W15" s="61"/>
       <c r="X15" s="57"/>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="40">
         <v>2017</v>
       </c>
@@ -2459,7 +2458,7 @@
         <v>8.24</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="38">
         <v>2016</v>
       </c>
@@ -2531,7 +2530,7 @@
         <v>8.44</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="40">
         <v>2015</v>
       </c>
@@ -2603,7 +2602,7 @@
         <v>7.58</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="38">
         <v>2014</v>
       </c>
@@ -2675,7 +2674,7 @@
         <v>9.01</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="40">
         <v>2013</v>
       </c>
@@ -2747,7 +2746,7 @@
         <v>5.64</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="38">
         <v>2012</v>
       </c>
@@ -2819,7 +2818,7 @@
         <v>5.13</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="40">
         <v>2011</v>
       </c>
@@ -2891,7 +2890,7 @@
         <v>8.23</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="38">
         <v>2010</v>
       </c>
@@ -2963,7 +2962,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="42">
         <v>2009</v>
       </c>
@@ -3035,7 +3034,7 @@
         <v>9.34</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="44"/>
       <c r="B25" s="45"/>
       <c r="C25" s="18" t="s">
@@ -3063,7 +3062,7 @@
       <c r="W25" s="51"/>
       <c r="X25" s="47"/>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="38">
         <v>2008</v>
       </c>
@@ -3135,7 +3134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="40">
         <v>2007</v>
       </c>
@@ -3207,7 +3206,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="38">
         <v>2006</v>
       </c>
@@ -3279,7 +3278,7 @@
         <v>8.35</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="40">
         <v>2005</v>
       </c>
@@ -3351,7 +3350,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="38">
         <v>2004</v>
       </c>
@@ -3423,7 +3422,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="40">
         <v>2003</v>
       </c>
@@ -3495,7 +3494,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="38">
         <v>2002</v>
       </c>
@@ -3567,7 +3566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="40" t="s">
         <v>54</v>
       </c>
